--- a/排课结果/软约束松弛总记录.xlsx
+++ b/排课结果/软约束松弛总记录.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>L3任课/教学班 覆盖 L2类别禁排</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'14403009.001@FA': '3,3', '14403009.001@FB': '2,2'} 守恒Σ=32=LLXS32</t>
+          <t>小数分段+连排放宽 守恒Σ=32=LLXS32</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'110000320.001@FA': '4,4', '110000320.001@FB': '3,3'} 守恒Σ=40=LLXS40</t>
+          <t>小数分段+连排放宽 守恒Σ=40=LLXS40</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'110000460.001@FA': '4,4', '110000460.001@FB': '3,3'} 守恒Σ=96=LLXS96</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'110000460.002@FA': '4,4', '110000460.002@FB': '3,3'} 守恒Σ=96=LLXS96</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'110000460.003@FA': '4,4', '110000460.003@FB': '3,3'} 守恒Σ=96=LLXS96</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'110000460.004@FA': '4,4', '110000460.004@FB': '3,3'} 守恒Σ=96=LLXS96</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'110000460.005@FA': '4,4', '110000460.005@FB': '3,3'} 守恒Σ=96=LLXS96</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3718,25 +3718,29 @@
           <t>110000460.006</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>高等数学b-2</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -3746,25 +3750,29 @@
           <t>110000480.001</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>高等数学c-2</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -3774,25 +3782,29 @@
           <t>110000480.002</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>高等数学c-2</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3826,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'110000640.017@FA': '4,4', '110000640.017@FB': '3,3'} 守恒Σ=56=LLXS56</t>
+          <t>小数分段+连排放宽 守恒Σ=56=LLXS56</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3846,12 +3858,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'110000670.001@FA': '4,4', '110000670.001@FB': '3,3'} 守恒Σ=96=LLXS96</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3866,25 +3878,29 @@
           <t>110000670.002</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>高等数学a-2</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -3894,25 +3910,29 @@
           <t>130000510.002</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -3922,25 +3942,29 @@
           <t>130000510.004</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -3950,25 +3974,29 @@
           <t>130000510.005</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -3978,25 +4006,29 @@
           <t>130000510.006</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -4006,25 +4038,29 @@
           <t>130000510.007</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -4034,25 +4070,29 @@
           <t>130000510.008</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -4062,25 +4102,29 @@
           <t>130000510.009</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -4090,25 +4134,29 @@
           <t>130000510.010</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4178,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>按可用天分大块·守恒零残差</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'14403010.001@FA': '3,3', '14403010.001@FB': '2,2'} 守恒Σ=32=LLXS32</t>
+          <t>小数分段+连排放宽 守恒Σ=32=LLXS32</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4147,27 +4195,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>17716055.001</t>
+          <t>15ALT016.003</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>短视频平台运营与用户增长</t>
+          <t>队田径业余队</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>连排放宽+小数分段</t>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>按周末天数分大块·守恒零残差</t>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>小数分段+周末大连排 {'17716055.001@FA': '3,3', '17716055.001@FB': '2,2'} 守恒Σ=32=LLXS32</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4179,26 +4227,670 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>17716055.001</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>短视频平台运营与用户增长</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>连排放宽+小数分段</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>按可用天分大块·守恒零残差</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>小数分段+连排放宽 守恒Σ=32=LLXS32</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>✅已排入</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>110010321.001</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>高等代数2</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>删被覆盖禁排段[] + 连排块[4, 4]</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>✅已排入</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>150130580.002</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>150130580.003</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>150130580.004</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>150130580.005</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>150130580.006</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
         <is>
           <t>连排放宽+小数分段</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>按周末天数分大块·守恒零残差</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>按可用天分大块·守恒零残差</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>@FA/@FB放宽后仍无解或不守恒(got=0,T=64)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>150130580.007</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>150130580.008</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>150130680.002</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>150130680.003</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>150130680.004</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>150130680.005</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>连排放宽+小数分段</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>按可用天分大块·守恒零残差</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>@FA/@FB放宽后仍无解或不守恒(got=0,T=96)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>150130680.006</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>连排放宽+小数分段</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>按可用天分大块·守恒零残差</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>@FA/@FB放宽后仍无解或不守恒(got=0,T=96)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>150140670.002</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>专项3</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>150140670.003</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>专项3</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>150140670.004</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>专项3</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>连排放宽+小数分段</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>按可用天分大块·守恒零残差</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>@FA/@FB放宽后仍无解或不守恒(got=0,T=64)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>150140760.002</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>专项5</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>150140760.003</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>专项5</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>150140760.004</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>专项5</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>151130120.001</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>乒乓球</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>类别禁排覆盖(L3&gt;L2)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>L3自身偏好 覆盖 低级摊平禁排</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>

--- a/排课结果/软约束松弛总记录.xlsx
+++ b/排课结果/软约束松弛总记录.xlsx
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
